--- a/portfolio_registry.xlsx
+++ b/portfolio_registry.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作品台账" sheetId="1" r:id="R891dc98f334e417b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R53b7d7790139497c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_下拉选项" sheetId="3" r:id="R9842eed0810444af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作品台账" sheetId="1" r:id="R1bba6d22d5d64142"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="Rb4f2e14c650d488e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_下拉选项" sheetId="3" r:id="R7720e481a1164d00"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -691,6 +691,12 @@
     <x:t xml:space="preserve">20260713-Wallpaper中文版.jpg</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">20260715-ELLEMEN睿士-被困在教培行业的清北毕业生年薪百万的神话已经过去了</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">被困在教培行业的清北毕业生：年薪百万的神话已经过去了</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">对话教培行业的清北毕业生：教培，是兜底、也是枷锁。</x:t>
   </x:si>
   <x:si>
@@ -700,7 +706,19 @@
     <x:t xml:space="preserve">#教育 #社会</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">[2026-07-15 18:11] 已整理入库</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">20260715-ELLEMEN睿士.png</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">爱马仕伦敦新邦德街的“爱马仕之家”，演绎英式“奇趣不羁”（eccentricity）设计的魅力。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://mp.weixin.qq.com/s/1G8hdr9ID8snELSeqki_rw</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">20260817-Wallpaper中文版.png</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">字段</x:t>
@@ -859,7 +877,7 @@
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="7"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -923,6 +941,9 @@
     </x:xf>
     <x:xf numFmtId="176" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="3">
@@ -2510,27 +2531,27 @@
         <x:v>225</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="45">
-      <x:c r="A32" s="19" t="str">
-        <x:v>20260715-ELLEMEN睿士-被困在教培行业的清北毕业生年薪百万的神话已经过去了</x:v>
-      </x:c>
-      <x:c r="B32" s="1" t="str">
-        <x:v>被困在教培行业的清北毕业生：年薪百万的神话已经过去了</x:v>
+    <x:row r="32" ht="90">
+      <x:c r="A32" s="19" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C32" s="20" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D32" s="19" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E32" s="19" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="F32" s="19" t="s">
         <x:v>82</x:v>
       </x:c>
       <x:c r="G32" s="20" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H32" s="20" t="s">
         <x:v>84</x:v>
@@ -2544,31 +2565,59 @@
       <x:c r="K32" s="19" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L32" s="19" t="str">
+      <x:c r="L32" s="19" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="M32" s="19" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="N32" s="20" t="s">
+        <x:v>232</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="45">
+      <x:c r="A33" s="8" t="str">
+        <x:v>20260817-Wallpaper中文版-由六栋保护建筑改造而成的伦敦爱马仕之家</x:v>
+      </x:c>
+      <x:c r="B33" s="22" t="str">
+        <x:v>由六栋保护建筑改造而成的伦敦爱马仕之家</x:v>
+      </x:c>
+      <x:c r="C33" s="22" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D33" s="8" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E33" s="8" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G33" s="22" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H33" s="20" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I33" s="11">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="J33" s="8" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K33" s="8" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L33" s="8" t="str">
         <x:v>已入库</x:v>
       </x:c>
-      <x:c r="M32" s="19" t="str">
-        <x:v>[2026-07-15 18:11] 已整理入库</x:v>
-      </x:c>
-      <x:c r="N32" s="20" t="s">
-        <x:v>229</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="8"/>
-      <x:c r="B33" s="8"/>
-      <x:c r="C33" s="8"/>
-      <x:c r="D33" s="8"/>
-      <x:c r="E33" s="8"/>
-      <x:c r="F33" s="8"/>
-      <x:c r="G33" s="8"/>
-      <x:c r="H33" s="8"/>
-      <x:c r="I33" s="11"/>
-      <x:c r="J33" s="8"/>
-      <x:c r="K33" s="8"/>
-      <x:c r="L33" s="8"/>
-      <x:c r="M33" s="8"/>
-      <x:c r="N33" s="8"/>
+      <x:c r="M33" s="8" t="str">
+        <x:v>[2026-08-17 22:49] 已整理入库</x:v>
+      </x:c>
+      <x:c r="N33" s="22" t="s">
+        <x:v>235</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="8"/>
@@ -10074,13 +10123,13 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="Rd1f49790e68348d1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="Rc182d0fdda6a48b0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="R22dadd719183414a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="Rbad54908ba4940e4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="R4c7a72e859234c4d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="Rba5aedd32ded47cf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="R27e28a1b04254582"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="Rcfeb951aef5241ea"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="R719ca26aa03c424f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="R222bd33352204be3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="Rd1bbaaff7cb74ef4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="Raa343de9db7e41fb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="R9dca36bc4f6d4f98"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="Rcb60e0e08f7d4551"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -10096,10 +10145,10 @@
   <x:sheetData>
     <x:row r="1" ht="16" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>230</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>231</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" customHeight="1">
@@ -10107,7 +10156,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>232</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
@@ -10115,7 +10164,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>233</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
@@ -10123,7 +10172,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="9" t="s">
-        <x:v>234</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
@@ -10131,7 +10180,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>235</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
@@ -10139,7 +10188,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>236</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
@@ -10147,7 +10196,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>237</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
@@ -10155,7 +10204,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>238</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
@@ -10163,7 +10212,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
@@ -10171,7 +10220,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>240</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" customHeight="1">
@@ -10179,7 +10228,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>241</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15">
@@ -10187,7 +10236,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>242</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -10217,7 +10266,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>243</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -10242,7 +10291,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="E3" t="s">
-        <x:v>244</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -10250,7 +10299,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="E4" t="s">
-        <x:v>245</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
